--- a/短线标的_2026-06-13.xlsx
+++ b/短线标的_2026-06-13.xlsx
@@ -8,6 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标的池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选概况" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬排除详情" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信号过滤详情" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略匹配详情" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分详情" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新闻筛查详情" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统告警" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,15 +40,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -52,11 +50,19 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +73,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,27 +108,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,26 +487,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -609,273 +602,59 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>中集集团</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>000039</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>超跌幅度适中+1</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sz000039.html</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>深圳华强</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>000062</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>-4.07</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>28.77</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>超跌幅度适中+1</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>28.77</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>27.62</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sz000062.html</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>皖维高新</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>600063</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>金融地产</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-4.39</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>超跌幅度适中+1</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600063.html</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>策略说明：</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>📊 共筛选出 3 只标的（A:0 B:3 C:0 D:0 E:0）</t>
+          <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>策略说明：</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 — 仓位10-15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策 — 仓位5-12%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位3-8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位8-15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -883,15 +662,251 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A3:R3"/>
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A5:R5"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>v6.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>数据日期</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>预测日期</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>原始标的池</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>硬排除</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>信号过滤</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>策略匹配</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>行业限制</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>新闻筛查</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>最终推荐</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>市场环境</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>强市_temp_A15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>策略分布</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>A:0 B:0 C:0 D:0 E:0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/短线标的_2026-06-13.xlsx
+++ b/短线标的_2026-06-13.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,27 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -47,10 +68,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -62,7 +79,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +90,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,20 +131,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -602,59 +637,275 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>浦发银行</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>600000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨幅1.26% 低换手0%</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600000.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>白云机场</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>600004</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨幅2.99% 低换手0%</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600004.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>宝钢股份</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>600019</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨幅2.91% 低换手0%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600019.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 3 只标的（A:0 B:139 C:0 D:0 E:0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -662,15 +913,20 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A3:R3"/>
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -685,146 +941,146 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>v6.5.2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>数据日期</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>预测日期</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>预测日期</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>原始标的池</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>硬排除</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>信号过滤</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>策略匹配</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>行业限制</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>新闻筛查</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>最终推荐</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>市场环境</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>强市_temp_A15</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>策略分布</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>A:0 B:0 C:0 D:0 E:0</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>A:0 B:139 C:0 D:0 E:0</t>
         </is>
       </c>
     </row>

--- a/短线标的_2026-06-13.xlsx
+++ b/短线标的_2026-06-13.xlsx
@@ -8,13 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标的池" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选概况" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬排除详情" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信号过滤详情" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略匹配详情" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分详情" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新闻筛查详情" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统告警" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选条件概述" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬排除明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信号过滤明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略匹配明细" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分明细" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新闻筛查" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键纪律" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <name val="Calibri"/>
@@ -44,13 +46,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -66,16 +62,22 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -131,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -139,23 +141,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -527,21 +533,21 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -637,7 +643,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -648,68 +654,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>浦发银行</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.26</v>
+        <v>-5.18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.5</v>
+        <v>16.64</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.67</v>
+        <v>15.56</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3.25</v>
+        <v>7.86</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>超跌反弹: 涨幅1.26% 低换手0%</t>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>9.67</v>
+        <v>15.56</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>14.94</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600000.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
+        <v>16.34</v>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600592.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -720,68 +726,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>白云机场</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600004</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2.99</v>
+        <v>-5.27</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>105.08</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8.26</v>
+        <v>97</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3.24</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>超跌反弹: 涨幅2.99% 低换手0%</t>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>8.26</v>
+        <v>97</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>7.93</v>
+        <v>93.12</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600004.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+        <v>101.85</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600487.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -792,128 +798,297 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宝钢股份</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600019</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.91</v>
+        <v>-4.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5.84</v>
+        <v>25.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6.02</v>
+        <v>24.39</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.62</v>
+        <v>6.81</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>超跌反弹: 涨幅2.91% 低换手0%</t>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>6.02</v>
+        <v>24.39</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5.78</v>
+        <v>23.41</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600019.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+        <v>25.61</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600234.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+    </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 3 只标的（A:0 B:139 C:0 D:0 E:0）</t>
-        </is>
-      </c>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>共筛选出 3 只标的（A:0 B:3 C:0 D:0 E:0）</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>策略说明：</t>
-        </is>
-      </c>
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="14" t="n"/>
+      <c r="P7" s="14" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
-        </is>
-      </c>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 -- 仓位强35-40%/震荡12-17%/弱关闭</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
-        </is>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>B 超跌反弹：连跌&gt;=3日，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 -- 仓位10-15%</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
-        </is>
-      </c>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策 -- 仓位5-12%</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
+      <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14" t="n"/>
+      <c r="R10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
-        </is>
-      </c>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% -- 仓位3-8%</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+      <c r="P11" s="14" t="n"/>
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>E 回调企稳突破：20日内创新高+回调MA20+/-3%+连3日缩量+站回MA5放量 -- 仓位8-15%</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
+      <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="14" t="n"/>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="14" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ 仅供参考，不构成投资建议</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>仅供参考，不构成投资建议</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="14" t="n"/>
+      <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A7:R7"/>
+  <mergeCells count="7">
     <mergeCell ref="A11:R11"/>
     <mergeCell ref="A10:R10"/>
     <mergeCell ref="A14:R14"/>
@@ -922,11 +1097,6 @@
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A12:R12"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -937,154 +1107,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>A股短线选股筛选条件 -- v6.5.1</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>v6.5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>v6.5.1</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>更新日期</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>预测日期</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>数据日期</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>预测日期</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>市场环境</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>总仓位上限</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>搜索预算</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>北向阈值</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>3000万</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>策略集中度上限</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>置信度仓位联动</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>启用</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>熔断阈值</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>筛选管道</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>原始标的池</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>硬排除</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>信号过滤</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>策略匹配</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>行业限制</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>新闻筛查</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>500只</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>硬排除后</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>200只</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>信号过滤后</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>35只</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>策略匹配后</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>15只</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>行业限制后</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>新闻筛查后</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>最终推荐</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>市场环境</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>策略分布</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>A:0 B:139 C:0 D:0 E:0</t>
-        </is>
-      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1095,9 +1412,4038 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>排除规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>600005</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>武钢股份</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.71&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>600008</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>首创环保</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.16&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>600010</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>包钢股份</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.39&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>600016</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>民生银行</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.63&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>600017</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>XD日照港</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.69&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>600020</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>中原高速</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.96&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>600022</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>山东钢铁</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.33&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>600028</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>中国石化</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.94&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>600033</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>福建高速</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.56&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>600035</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>楚天高速</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.79&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>600050</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>中国联通</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.37&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>600052</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>东望时代</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.65&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>600053</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>*ST九鼎</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>600067</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>冠城新材</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.48&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>600069</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>退市银鸽</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.28&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>600070</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>*ST富润</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.42&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>600074</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>退市保千</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.17&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>600075</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>新疆天业</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.75&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>600076</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>康欣新材</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.47&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>600077</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>*ST宋都</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>600079</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ST人福</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>600080</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>ST金花</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.78&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>600082</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ST海泰</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.05&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>600083</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>*ST博信</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.92&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>600084</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>*ST尼雅</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.27&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>600086</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>退市金钰</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.16&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>600090</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>退市济堂</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.27&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>600091</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>退市明科</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.76&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>600093</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>退市易见</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.50&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>600094</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>大名城</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>600103</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>青山纸业</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.50&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>600107</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>*ST尔雅</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>600108</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>亚盛集团</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.59&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>600112</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>*ST天成</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.73&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>600115</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>中国东航</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>600117</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>西宁特钢</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.27&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>600119</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>*ST长投</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.84&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>600120</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>浙江东方</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.47&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>600121</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>郑州煤电</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.51&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>600122</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>*ST宏图</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.38&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>600130</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>波导股份</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.53&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>600136</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>ST明诚</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.47&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>600139</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>*ST西源</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.74&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>600145</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>退市新亿</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.34&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>600146</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>退市环球</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.22&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>600157</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>永泰能源</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.70&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>600159</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>大龙地产</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.63&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>600162</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>香江控股</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.47&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>600163</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>中闽能源</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则12:涨幅9.7%&gt;7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>600165</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>ST宁科</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.83&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>600166</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>福田汽车</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.10&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>600168</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>武汉控股</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.46&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>600169</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>ST太重</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.24&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>600170</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>上海建工</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.42&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>600175</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>退市美都</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.21&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>600179</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>安通控股</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.56&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>600180</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>*ST瑞茂</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.32&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>600183</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>生益科技</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则4:股价151.28&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>600187</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>*ST国中</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.52&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>600190</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>退市锦港</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.63&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>600193</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>退市创兴</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.16&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>600200</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>退市苏吴</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.29&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>600208</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>衢州发展</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.97&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>600209</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>退市罗顿</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.18&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>600213</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>*ST亚星</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>600217</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>中再资环</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.15&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>600219</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>南山铝业</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.73&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>600220</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>ST阳光</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.37&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>600221</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>海航控股</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.53&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>600225</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>退市卓朗</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.29&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>600227</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>赤天化</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.87&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>600229</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>城市传媒</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>600231</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>凌钢股份</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.89&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>600238</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>*ST椰岛</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.91&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>600239</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>ST云城</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.42&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>600240</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>退市华业</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>600242</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>退市中昌</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.25&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>600243</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>*ST海华</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.02&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>600247</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>*ST成城</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.65&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>600248</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>陕建股份</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.02&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>600252</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>中恒集团</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.16&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>600255</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>鑫科材料</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.15&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>600260</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>*ST凯乐</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.47&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>600261</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>阳光照明</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.19&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>600265</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>*ST景谷</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>600266</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>城建发展</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.43&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>600269</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>赣粤高速</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.20&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>600275</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>退市昌鱼</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>600277</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>ST亿利</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.38&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>600279</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>重庆港</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.44&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>600280</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>中央商场</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.93&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>600281</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>华阳新材</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>600282</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>南钢股份</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.84&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>600287</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>苏豪时尚</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>600289</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>ST信通</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>600290</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>*ST华仪</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.37&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>600291</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>退市西水</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.89&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>600292</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>电投水电</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>600293</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>三峡新材</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>600297</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>广汇汽车</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.78&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>600300</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>维维股份</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.07&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>600301</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>华锡有色</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则12:涨幅7.6%&gt;7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>600302</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>ST标准</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>600303</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>曙光股份</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.04&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>600306</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>退市商城</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.29&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>600307</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>酒钢宏兴</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.57&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>600308</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>华泰股份</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.36&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>600310</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>广西能源</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.63&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>600311</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>*ST荣华</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.61&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>600317</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>营口港</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.60&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>600320</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>振华重工</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.40&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>600321</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>正源股份</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.50&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>600322</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>津投城开</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.68&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>600325</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>华发股份</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.63&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>600327</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>大东方</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.50&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>600337</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>ST美克</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>600339</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>中油工程</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.31&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>600340</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>*ST华幸</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.33&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>600346</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>恒力石化</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>600355</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>*ST精伦</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.58&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>600361</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>创新新材</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.13&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>600362</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>江西铜业</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>600365</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>ST通葡</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.55&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>600368</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>五洲交通</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.78&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>600369</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>西南证券</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.99&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>600370</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>*ST三房</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.46&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>600375</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>汉马科技</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.94&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>600376</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>首开股份</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.40&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>600378</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>XD昊华科</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则22:跌停-10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>600381</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>*ST春天</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>600383</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>金地集团</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.51&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>600385</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>退市金泰</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.20&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>600386</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>北巴传媒</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.50&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>600387</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>退市海越</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.94&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>600390</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>五矿资本</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.65&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>600391</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>航发科技</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>600393</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>ST粤泰</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.37&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>600399</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>抚顺特钢</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.32&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>600400</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>红豆股份</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.61&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>600401</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>退市海润</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.15&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>600403</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>大有能源</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则22:跌停-9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>600405</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>动力源</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.26&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>600408</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>安泰集团</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.88&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>600421</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>退市华嵘</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.26&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>600423</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>*ST柳化</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.48&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>600425</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>XD青松建</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.54&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>600429</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>三元股份</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.40&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>600432</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>退市吉恩</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.38&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>600433</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>冠豪高新</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.53&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>600436</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>片仔癀</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则4:股价119.56&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>600439</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>瑞贝卡</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.27&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>600448</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>华纺股份</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.90&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>600462</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>退市九有</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.21&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>600466</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>*ST蓝光</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.40&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>600467</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>好当家</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.19&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>600476</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>*ST湘邮</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则5:ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>600477</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>杭萧钢构</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.59&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>600485</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>*ST信威</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.39&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>600488</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.76&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>600491</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>ST龙元</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.31&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>600495</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>晋西车轴</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.80&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>600496</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>精工钢构</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.84&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>600497</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>驰宏锌锗</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>600500</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>中化国际</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>600502</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>安徽建工</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.68&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>600503</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>华丽家族</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.46&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>600507</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>方大特钢</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.29&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>600512</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>腾达建设</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.08&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>600515</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>海南机场</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.98&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>600517</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>国网英大</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.89&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>600518</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>康美药业</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.40&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>600519</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则4:股价1291.91&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>600525</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>ST长园</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.99&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>600526</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>菲达环保</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.49&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>600527</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>江南高纤</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.32&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>600531</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>豫光金铅</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>600532</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>退市未来</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.72&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>600533</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>栖霞建设</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.19&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>600536</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>中国软件</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则22:跌停-10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>600537</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>*ST亿晶</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.58&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>600539</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>狮头股份</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>600540</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>新赛股份</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.46&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>600543</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>*ST莫高</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.22&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>600555</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>退市海创</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.26&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>600556</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>天下秀</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.89&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>600563</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>XD法拉电</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则4:股价143.00&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>600565</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>ST迪马</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.85&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>600567</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>山鹰国际</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.44&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>600568</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>ST中珠</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.54&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>600569</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>安阳钢铁</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价1.87&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>600572</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>康恩贝</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.13&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>600575</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>淮河能源</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.99&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>600576</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>祥源文旅</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>600581</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>*ST八钢</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价2.57&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>600586</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>金晶科技</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.57&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>600594</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>益佰制药</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价3.29&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>600599</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>退市熊猫</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>600601</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>方正科技</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>600603</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
+          <t>广汇物流</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.64&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
+        <is>
+          <t>600604</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>市北高新</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.22&lt;5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,9 +5454,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>信号过滤明细</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>共触发信号过滤 4 项</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n"/>
+      <c r="B3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>假动量高开</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>13次</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>缩量涨停</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>12次</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>诱多</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>10次</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>振幅&gt;15%</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>1次</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1121,9 +5536,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>量比</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>策略原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>600592</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>跌5.2%(简版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>跌5.3%(简版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>600234</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>跌4.5%(简版)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1134,9 +5698,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>基础分</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>总分</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>置信度</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>预测逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>600592</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>600234</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1147,9 +5872,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>新闻筛查结果</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n"/>
+      <c r="B3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>通过标的新闻备注:</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>600592 龙溪股份</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>600487 亨通光电</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>600234 科新发展</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1160,9 +5954,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>关键纪律 -- v6.5.1</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>步骤零每次先于一切执行</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>网络授时北京时间优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>不追高</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>涨停(&gt;9.8%)/涨&gt;7%排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>同行业&lt;=3只</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>申万一级行业集中度控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>已持仓排除</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>7日内已推荐+已持仓排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>五级管道</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>硬排除31项-&gt;信号过滤14项-&gt;5策略-&gt;行业限制-&gt;新闻筛查</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>全市场API</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>东方财富clist一次性拉取，降级新浪API</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Excel格式化</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>openpyxl红涨绿跌+策略色+置信度色</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>仅供参考</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>不构成投资建议</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/短线标的_2026-06-13.xlsx
+++ b/短线标的_2026-06-13.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,11 +50,6 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,19 +157,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -542,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -668,12 +660,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>精达股份</t>
+          <t>鹏欣资源</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600577</t>
+          <t>600490</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -687,19 +679,19 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>6.45</v>
+        <v>6.93</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11.02</v>
+        <v>6.81</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11.55</v>
+        <v>7.1</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7.37</v>
+        <v>6.02</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -715,17 +707,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.55</v>
+        <v>7.1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>11.09</v>
+        <v>6.82</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>12.13</v>
+        <v>7.46</v>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600577.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600490.html</t>
         </is>
       </c>
     </row>
@@ -740,12 +732,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>航天动力</t>
+          <t>浙江龙盛</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600343</t>
+          <t>600352</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -759,19 +751,19 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.27</v>
+        <v>6.8</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>24.08</v>
+        <v>10.98</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.08</v>
+        <v>11.46</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>8.69</v>
+        <v>7.92</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -787,17 +779,17 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>25.08</v>
+        <v>11.46</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>24.08</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>26.33</v>
+        <v>12.03</v>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600343.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600352.html</t>
         </is>
       </c>
     </row>
@@ -812,12 +804,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>华鲁恒升</t>
+          <t>万华化学</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600426</t>
+          <t>600309</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -831,19 +823,19 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6.1</v>
+        <v>6.73</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>26.57</v>
+        <v>67.2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.33</v>
+        <v>71.67</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>10.22</v>
+        <v>8.98</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -859,233 +851,233 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>28.33</v>
+        <v>71.67</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>27.2</v>
+        <v>68.8</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>29.75</v>
+        <v>75.25</v>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600426.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600309.html</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>浙江医药</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>600216</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>医药生物</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>国金证券</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>600109</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>非银金融</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>超跌反弹</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>9</v>
+      <c r="K5" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>动量延续</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="O5" s="6" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600216.html</t>
+      <c r="O5" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600109.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>上海电力</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>600021</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>南方航空</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>600029</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>超跌反弹</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>9</v>
+      <c r="K6" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>动量延续</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="O6" s="6" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600021.html</t>
+      <c r="O6" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600029.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>浙能电力</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>600023</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>中金黄金</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>600489</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>超跌反弹</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>9</v>
+      <c r="K7" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>动量延续</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="O7" s="6" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600023.html</t>
+      <c r="O7" s="2" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600489.html</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1092,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>西昌电力</t>
+          <t>涪陵电力</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>600505</t>
+          <t>600452</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1118,20 +1110,20 @@
           <t>公用事业</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>-1.41</v>
+      <c r="G8" s="7" t="n">
+        <v>2.93</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>14.35</v>
+        <v>10.4</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>14.65</v>
+        <v>10.55</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>6.66</v>
+        <v>5.37</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1147,73 +1139,433 @@
         </is>
       </c>
       <c r="O8" s="6" t="n">
-        <v>14.65</v>
+        <v>10.55</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>14.06</v>
+        <v>10.13</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>15.38</v>
+        <v>11.08</v>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600505.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 7 只标的（A:3 B:4 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+          <t>https://quote.eastmoney.com/concept/sh600452.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>光明乳业</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>600597</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>超跌反弹</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600597.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>复星医药</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>600196</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>超跌反弹</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600196.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>中国医药</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>600056</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>超跌反弹</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600056.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>浙江医药</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>600216</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>超跌反弹</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600216.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>首旅酒店</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>600258</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>酒店</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>社会服务</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>超跌反弹</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600258.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 12 只标的（A:6 B:6 C:0 D:0 E:0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -1221,14 +1573,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A20:R20"/>
+    <mergeCell ref="A21:R21"/>
     <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A19:R19"/>
+    <mergeCell ref="A17:R17"/>
+    <mergeCell ref="A23:R23"/>
     <mergeCell ref="A18:R18"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="A14:R14"/>
-    <mergeCell ref="A12:R12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
